--- a/ecoconception/Carte_systeme.xlsx
+++ b/ecoconception/Carte_systeme.xlsx
@@ -55,7 +55,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>00.00.004</t>
+    <t>00.00.005</t>
   </si>
   <si>
     <t>Last change</t>
@@ -1103,7 +1103,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="n" s="2">
-        <v>46140.541334525464</v>
+        <v>46141.530195671294</v>
       </c>
     </row>
     <row r="8">
@@ -2575,7 +2575,7 @@
         <v>54</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>0.355</v>
+        <v>3.18</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>55</v>
